--- a/artifacts/results/Hiretest/analysis_5to6.xlsx
+++ b/artifacts/results/Hiretest/analysis_5to6.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="版本报告" sheetId="1" r:id="R10fc0bc579a14dd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Version Report" sheetId="1" r:id="Rf4953aa6042549c1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -344,7 +344,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>匿名学生</x:v>
+        <x:v>Anonymous Student</x:v>
       </x:c>
       <x:c r="B1" s="1" t="inlineStr">
         <x:is>
